--- a/data/trans_orig/Q17H_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17H_R-Habitat-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,29</t>
+          <t>1,03; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,06</t>
+          <t>0,77; 1,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,79</t>
+          <t>0,57; 0,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,68</t>
+          <t>0,51; 0,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,03</t>
+          <t>0,84; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,83</t>
+          <t>0,66; 0,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,2</t>
+          <t>0,95; 1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,01</t>
+          <t>0,8; 1,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,72</t>
+          <t>0,58; 0,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 0,95</t>
+          <t>0,79; 0,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,08; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,24</t>
+          <t>0,93; 1,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,27 +912,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,03</t>
+          <t>0,75; 1,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,05</t>
+          <t>0,56; 1,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,27</t>
+          <t>0,23; 0,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,13</t>
+          <t>0,95; 1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,06</t>
+          <t>0,78; 1,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,41</t>
+          <t>1,05; 1,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,23</t>
+          <t>0,91; 1,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,84</t>
+          <t>0,69; 0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,68</t>
+          <t>0,51; 0,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,91</t>
+          <t>0,72; 0,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,23</t>
+          <t>1,08; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,05</t>
+          <t>0,9; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,67</t>
+          <t>0,55; 0,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,84</t>
+          <t>0,74; 0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
